--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87379</v>
+        <v>87385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87472</v>
+        <v>87478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87472</v>
+        <v>87478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87472</v>
+        <v>87478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87327</v>
+        <v>87333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87516</v>
+        <v>87522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109275</v>
       </c>
       <c r="B8" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109277</v>
       </c>
       <c r="B9" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109280</v>
       </c>
       <c r="B10" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109289</v>
       </c>
       <c r="B11" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109302</v>
       </c>
       <c r="B12" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109311</v>
       </c>
       <c r="B13" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109314</v>
       </c>
       <c r="B14" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109273</v>
       </c>
       <c r="B15" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109288</v>
       </c>
       <c r="B16" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109294</v>
       </c>
       <c r="B17" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109308</v>
       </c>
       <c r="B18" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109291</v>
       </c>
       <c r="B19" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109293</v>
       </c>
       <c r="B20" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>137109299</v>
       </c>
       <c r="B21" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109300</v>
       </c>
       <c r="B22" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109301</v>
       </c>
       <c r="B23" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109304</v>
       </c>
       <c r="B24" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109306</v>
       </c>
       <c r="B25" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109307</v>
       </c>
       <c r="B26" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109310</v>
       </c>
       <c r="B27" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109312</v>
       </c>
       <c r="B28" t="n">
-        <v>87574</v>
+        <v>87580</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109278</v>
       </c>
       <c r="B29" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109279</v>
       </c>
       <c r="B30" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109281</v>
       </c>
       <c r="B31" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109285</v>
       </c>
       <c r="B32" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109295</v>
       </c>
       <c r="B33" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109274</v>
       </c>
       <c r="B34" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109282</v>
       </c>
       <c r="B35" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109290</v>
       </c>
       <c r="B36" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109276</v>
       </c>
       <c r="B37" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109298</v>
       </c>
       <c r="B38" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109283</v>
       </c>
       <c r="B39" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109286</v>
       </c>
       <c r="B40" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109296</v>
       </c>
       <c r="B41" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87385</v>
+        <v>87389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87478</v>
+        <v>87482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87478</v>
+        <v>87482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87478</v>
+        <v>87482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87333</v>
+        <v>87337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87522</v>
+        <v>87526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137109275</v>
+        <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697085</v>
+        <v>696843</v>
       </c>
       <c r="R8" t="n">
-        <v>6382862</v>
+        <v>6382731</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Träkumla</t>
+          <t>Stenkumla</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,12 +1471,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109275</t>
+          <t>https://artportalen.se/Sighting/137109071</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137109277</v>
+        <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697064</v>
+        <v>696831</v>
       </c>
       <c r="R9" t="n">
-        <v>6382853</v>
+        <v>6382738</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Träkumla</t>
+          <t>Stenkumla</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,12 +1587,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1602,16 +1602,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109277</t>
+          <t>https://artportalen.se/Sighting/137109073</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137109280</v>
+        <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696984</v>
+        <v>696796</v>
       </c>
       <c r="R10" t="n">
-        <v>6382814</v>
+        <v>6382739</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,12 +1703,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1718,16 +1718,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109280</t>
+          <t>https://artportalen.se/Sighting/137109079</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137109289</v>
+        <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,13 +1759,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696873</v>
+        <v>696804</v>
       </c>
       <c r="R11" t="n">
-        <v>6382801</v>
+        <v>6382715</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,12 +1819,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1834,16 +1834,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109289</t>
+          <t>https://artportalen.se/Sighting/137109081</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137109302</v>
+        <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696822</v>
+        <v>697085</v>
       </c>
       <c r="R12" t="n">
-        <v>6382732</v>
+        <v>6382862</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Stenkumla</t>
+          <t>Träkumla</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,16 +1950,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109302</t>
+          <t>https://artportalen.se/Sighting/137109275</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137109311</v>
+        <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696902</v>
+        <v>697064</v>
       </c>
       <c r="R13" t="n">
-        <v>6382732</v>
+        <v>6382853</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Stenkumla</t>
+          <t>Träkumla</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,16 +2066,16 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109311</t>
+          <t>https://artportalen.se/Sighting/137109277</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137109314</v>
+        <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696976</v>
+        <v>696984</v>
       </c>
       <c r="R14" t="n">
-        <v>6382778</v>
+        <v>6382814</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,16 +2182,16 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109314</t>
+          <t>https://artportalen.se/Sighting/137109280</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137109273</v>
+        <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87335</v>
+        <v>87502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697102</v>
+        <v>696873</v>
       </c>
       <c r="R15" t="n">
-        <v>6382882</v>
+        <v>6382801</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Träkumla</t>
+          <t>Stenkumla</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,16 +2298,16 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109273</t>
+          <t>https://artportalen.se/Sighting/137109289</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137109288</v>
+        <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87335</v>
+        <v>87502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696875</v>
+        <v>696822</v>
       </c>
       <c r="R16" t="n">
-        <v>6382804</v>
+        <v>6382732</v>
       </c>
       <c r="S16" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,16 +2414,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109288</t>
+          <t>https://artportalen.se/Sighting/137109302</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137109294</v>
+        <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87335</v>
+        <v>87502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,21 +2431,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696865</v>
+        <v>696902</v>
       </c>
       <c r="R17" t="n">
-        <v>6382768</v>
+        <v>6382732</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,16 +2530,16 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109294</t>
+          <t>https://artportalen.se/Sighting/137109311</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137109308</v>
+        <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87335</v>
+        <v>87502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696822</v>
+        <v>696976</v>
       </c>
       <c r="R18" t="n">
-        <v>6382732</v>
+        <v>6382778</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,38 +2646,38 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109308</t>
+          <t>https://artportalen.se/Sighting/137109314</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137109291</v>
+        <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87580</v>
+        <v>87339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696871</v>
+        <v>696843</v>
       </c>
       <c r="R19" t="n">
-        <v>6382784</v>
+        <v>6382731</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,12 +2747,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2762,38 +2762,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109291</t>
+          <t>https://artportalen.se/Sighting/137109069</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137109293</v>
+        <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87580</v>
+        <v>87339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696870</v>
+        <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382781</v>
+        <v>6382882</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Stenkumla</t>
+          <t>Träkumla</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2878,38 +2878,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109293</t>
+          <t>https://artportalen.se/Sighting/137109273</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137109299</v>
+        <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87580</v>
+        <v>87339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,13 +2919,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696839</v>
+        <v>696875</v>
       </c>
       <c r="R21" t="n">
-        <v>6382743</v>
+        <v>6382804</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,38 +2994,38 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109299</t>
+          <t>https://artportalen.se/Sighting/137109288</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137109300</v>
+        <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87580</v>
+        <v>87339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696835</v>
+        <v>696865</v>
       </c>
       <c r="R22" t="n">
-        <v>6382731</v>
+        <v>6382768</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,38 +3110,38 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109300</t>
+          <t>https://artportalen.se/Sighting/137109294</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137109301</v>
+        <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87580</v>
+        <v>87339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696824</v>
+        <v>696822</v>
       </c>
       <c r="R23" t="n">
-        <v>6382729</v>
+        <v>6382732</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,16 +3226,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109301</t>
+          <t>https://artportalen.se/Sighting/137109308</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137109304</v>
+        <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696807</v>
+        <v>696835</v>
       </c>
       <c r="R24" t="n">
-        <v>6382748</v>
+        <v>6382743</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,12 +3327,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3342,16 +3342,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109304</t>
+          <t>https://artportalen.se/Sighting/137109067</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137109306</v>
+        <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696792</v>
+        <v>697074</v>
       </c>
       <c r="R25" t="n">
-        <v>6382743</v>
+        <v>6382772</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Stenkumla</t>
+          <t>Träkumla</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,12 +3443,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3458,16 +3458,16 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109306</t>
+          <t>https://artportalen.se/Sighting/137109086</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137109307</v>
+        <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696810</v>
+        <v>696871</v>
       </c>
       <c r="R26" t="n">
-        <v>6382739</v>
+        <v>6382784</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,16 +3574,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109307</t>
+          <t>https://artportalen.se/Sighting/137109291</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137109310</v>
+        <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696895</v>
+        <v>696870</v>
       </c>
       <c r="R27" t="n">
-        <v>6382729</v>
+        <v>6382781</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3690,16 +3690,16 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109310</t>
+          <t>https://artportalen.se/Sighting/137109293</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137109312</v>
+        <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696910</v>
+        <v>696839</v>
       </c>
       <c r="R28" t="n">
         <v>6382743</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3806,38 +3806,38 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109312</t>
+          <t>https://artportalen.se/Sighting/137109299</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137109278</v>
+        <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>93094</v>
+        <v>87584</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697052</v>
+        <v>696835</v>
       </c>
       <c r="R29" t="n">
-        <v>6382852</v>
+        <v>6382731</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Träkumla</t>
+          <t>Stenkumla</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3922,38 +3922,38 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109278</t>
+          <t>https://artportalen.se/Sighting/137109300</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137109279</v>
+        <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>93094</v>
+        <v>87584</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697010</v>
+        <v>696824</v>
       </c>
       <c r="R30" t="n">
-        <v>6382836</v>
+        <v>6382729</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Träkumla</t>
+          <t>Stenkumla</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4038,38 +4038,38 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109279</t>
+          <t>https://artportalen.se/Sighting/137109301</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137109281</v>
+        <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>93094</v>
+        <v>87584</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696988</v>
+        <v>696807</v>
       </c>
       <c r="R31" t="n">
-        <v>6382832</v>
+        <v>6382748</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4154,38 +4154,38 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109281</t>
+          <t>https://artportalen.se/Sighting/137109304</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137109285</v>
+        <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>93094</v>
+        <v>87584</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696902</v>
+        <v>696792</v>
       </c>
       <c r="R32" t="n">
-        <v>6382883</v>
+        <v>6382743</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4270,38 +4270,38 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109285</t>
+          <t>https://artportalen.se/Sighting/137109306</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137109295</v>
+        <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>93094</v>
+        <v>87584</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696855</v>
+        <v>696810</v>
       </c>
       <c r="R33" t="n">
-        <v>6382750</v>
+        <v>6382739</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4386,38 +4386,38 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109295</t>
+          <t>https://artportalen.se/Sighting/137109307</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137109274</v>
+        <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>93460</v>
+        <v>87584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>3767</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4427,13 +4427,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697094</v>
+        <v>696895</v>
       </c>
       <c r="R34" t="n">
-        <v>6382875</v>
+        <v>6382729</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Träkumla</t>
+          <t>Stenkumla</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4502,38 +4502,38 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109274</t>
+          <t>https://artportalen.se/Sighting/137109310</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137109282</v>
+        <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>93460</v>
+        <v>87584</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>3767</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696957</v>
+        <v>696910</v>
       </c>
       <c r="R35" t="n">
-        <v>6382887</v>
+        <v>6382743</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4618,38 +4618,38 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109282</t>
+          <t>https://artportalen.se/Sighting/137109312</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137109290</v>
+        <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93460</v>
+        <v>93098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4659,13 +4659,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696870</v>
+        <v>697052</v>
       </c>
       <c r="R36" t="n">
-        <v>6382794</v>
+        <v>6382852</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Stenkumla</t>
+          <t>Träkumla</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4734,38 +4734,38 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109290</t>
+          <t>https://artportalen.se/Sighting/137109278</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137109276</v>
+        <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>87451</v>
+        <v>93098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>248956</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697062</v>
+        <v>697010</v>
       </c>
       <c r="R37" t="n">
-        <v>6382872</v>
+        <v>6382836</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4850,38 +4850,38 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109276</t>
+          <t>https://artportalen.se/Sighting/137109279</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137109298</v>
+        <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>87451</v>
+        <v>93098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>248956</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4891,13 +4891,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696847</v>
+        <v>696988</v>
       </c>
       <c r="R38" t="n">
-        <v>6382740</v>
+        <v>6382832</v>
       </c>
       <c r="S38" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4966,38 +4966,38 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109298</t>
+          <t>https://artportalen.se/Sighting/137109281</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137109283</v>
+        <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>87535</v>
+        <v>93098</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696906</v>
+        <v>696902</v>
       </c>
       <c r="R39" t="n">
-        <v>6382884</v>
+        <v>6382883</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5082,38 +5082,38 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109283</t>
+          <t>https://artportalen.se/Sighting/137109285</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137109286</v>
+        <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>87535</v>
+        <v>93098</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696884</v>
+        <v>696855</v>
       </c>
       <c r="R40" t="n">
-        <v>6382856</v>
+        <v>6382750</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5198,16 +5198,16 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109286</t>
+          <t>https://artportalen.se/Sighting/137109295</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137109296</v>
+        <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>87535</v>
+        <v>93464</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696848</v>
+        <v>696950</v>
       </c>
       <c r="R41" t="n">
-        <v>6382745</v>
+        <v>6382880</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5299,12 +5299,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5313,6 +5313,1398 @@
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109055</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137109061</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93464</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>696884</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6382816</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109061</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137109083</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93464</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>697058</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6382785</v>
+      </c>
+      <c r="S43" t="n">
+        <v>16</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Träkumla</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109083</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137109274</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93464</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>697094</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6382875</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Träkumla</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109274</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137109282</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93464</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>696957</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6382887</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109282</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137109290</v>
+      </c>
+      <c r="B46" t="n">
+        <v>93464</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>696870</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6382794</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109290</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137109052</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>697102</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6382882</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Träkumla</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109052</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137109053</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87455</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>697071</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6382866</v>
+      </c>
+      <c r="S48" t="n">
+        <v>8</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Träkumla</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109053</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137109276</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87455</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>697062</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6382872</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Träkumla</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109276</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137109298</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87455</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>696847</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6382740</v>
+      </c>
+      <c r="S50" t="n">
+        <v>14</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109298</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137109283</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>696906</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6382884</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109283</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137109286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>696884</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6382856</v>
+      </c>
+      <c r="S52" t="n">
+        <v>11</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109286</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137109296</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>696848</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6382745</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137109296</t>
         </is>
@@ -5360,6 +6752,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6364,7 +6364,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137109283</v>
+        <v>137109059</v>
       </c>
       <c r="B51" t="n">
         <v>87539</v>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696906</v>
+        <v>696921</v>
       </c>
       <c r="R51" t="n">
-        <v>6382884</v>
+        <v>6382889</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6453,18 +6453,19 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6474,13 +6475,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109283</t>
+          <t>https://artportalen.se/Sighting/137109059</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137109286</v>
+        <v>137109063</v>
       </c>
       <c r="B52" t="n">
         <v>87539</v>
@@ -6515,13 +6516,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696884</v>
+        <v>696882</v>
       </c>
       <c r="R52" t="n">
-        <v>6382856</v>
+        <v>6382809</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6550,7 +6551,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6561,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6569,18 +6570,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6590,13 +6592,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109286</t>
+          <t>https://artportalen.se/Sighting/137109063</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137109296</v>
+        <v>137109075</v>
       </c>
       <c r="B53" t="n">
         <v>87539</v>
@@ -6631,10 +6633,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696848</v>
+        <v>696833</v>
       </c>
       <c r="R53" t="n">
-        <v>6382745</v>
+        <v>6382735</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6666,7 +6668,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6676,7 +6678,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6685,18 +6687,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6705,6 +6708,471 @@
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109075</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137109077</v>
+      </c>
+      <c r="B54" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>696814</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6382742</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109077</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137109283</v>
+      </c>
+      <c r="B55" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>696906</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6382884</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109283</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137109286</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>696884</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6382856</v>
+      </c>
+      <c r="S56" t="n">
+        <v>11</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109286</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137109296</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>696848</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6382745</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137109296</t>
         </is>
@@ -6764,6 +7232,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87389</v>
+        <v>87391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87482</v>
+        <v>87484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87482</v>
+        <v>87484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87482</v>
+        <v>87484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87337</v>
+        <v>87339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87526</v>
+        <v>87528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87391</v>
+        <v>87404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87484</v>
+        <v>87497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87484</v>
+        <v>87497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87484</v>
+        <v>87497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87339</v>
+        <v>87352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87528</v>
+        <v>87541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87404</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87352</v>
+        <v>87354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87541</v>
+        <v>87543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87354</v>
+        <v>87357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87543</v>
+        <v>87546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87409</v>
+        <v>87419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87357</v>
+        <v>87367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87546</v>
+        <v>87556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87419</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87367</v>
+        <v>87368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87556</v>
+        <v>87557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87368</v>
+        <v>87371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87423</v>
+        <v>87428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87371</v>
+        <v>87376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87560</v>
+        <v>87565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87428</v>
+        <v>87439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87376</v>
+        <v>87387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87565</v>
+        <v>87576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87439</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87387</v>
+        <v>87388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87576</v>
+        <v>87577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382883</v>
+        <v>6382882</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87388</v>
+        <v>87391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87577</v>
+        <v>87580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42201-2023 artfynd.xlsx
+++ b/artfynd/A 42201-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109292</v>
       </c>
       <c r="B2" t="n">
-        <v>87443</v>
+        <v>87447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137109287</v>
       </c>
       <c r="B3" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137109305</v>
       </c>
       <c r="B4" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137109315</v>
       </c>
       <c r="B5" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137109297</v>
       </c>
       <c r="B6" t="n">
-        <v>87391</v>
+        <v>87395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137109303</v>
       </c>
       <c r="B7" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137109071</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>137109073</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137109079</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137109081</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>137109275</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137109277</v>
       </c>
       <c r="B13" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137109280</v>
       </c>
       <c r="B14" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>137109289</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137109302</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137109311</v>
       </c>
       <c r="B17" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>137109314</v>
       </c>
       <c r="B18" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>137109069</v>
       </c>
       <c r="B19" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137109273</v>
       </c>
       <c r="B20" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>697102</v>
       </c>
       <c r="R20" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2887,7 +2887,7 @@
         <v>137109288</v>
       </c>
       <c r="B21" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137109294</v>
       </c>
       <c r="B22" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>137109308</v>
       </c>
       <c r="B23" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137109067</v>
       </c>
       <c r="B24" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>137109086</v>
       </c>
       <c r="B25" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>137109291</v>
       </c>
       <c r="B26" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137109293</v>
       </c>
       <c r="B27" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137109299</v>
       </c>
       <c r="B28" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>137109300</v>
       </c>
       <c r="B29" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137109301</v>
       </c>
       <c r="B30" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>137109304</v>
       </c>
       <c r="B31" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>137109306</v>
       </c>
       <c r="B32" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137109307</v>
       </c>
       <c r="B33" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>137109310</v>
       </c>
       <c r="B34" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>137109312</v>
       </c>
       <c r="B35" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137109278</v>
       </c>
       <c r="B36" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>137109279</v>
       </c>
       <c r="B37" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137109281</v>
       </c>
       <c r="B38" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>137109285</v>
       </c>
       <c r="B39" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>137109295</v>
       </c>
       <c r="B40" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>137109055</v>
       </c>
       <c r="B41" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>137109061</v>
       </c>
       <c r="B42" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>137109083</v>
       </c>
       <c r="B43" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>137109274</v>
       </c>
       <c r="B44" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>137109282</v>
       </c>
       <c r="B45" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>137109290</v>
       </c>
       <c r="B46" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137109052</v>
       </c>
       <c r="B47" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>697102</v>
       </c>
       <c r="R47" t="n">
-        <v>6382882</v>
+        <v>6382883</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>137109053</v>
       </c>
       <c r="B48" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137109276</v>
       </c>
       <c r="B49" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>137109298</v>
       </c>
       <c r="B50" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>137109059</v>
       </c>
       <c r="B51" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>137109063</v>
       </c>
       <c r="B52" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>137109075</v>
       </c>
       <c r="B53" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>137109077</v>
       </c>
       <c r="B54" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>137109283</v>
       </c>
       <c r="B55" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>137109286</v>
       </c>
       <c r="B56" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137109296</v>
       </c>
       <c r="B57" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
